--- a/customer_registration_forms/034_cosmetology_client_consultation_form--customer_registration_forms.xlsx
+++ b/customer_registration_forms/034_cosmetology_client_consultation_form--customer_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
     <col width="29" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -528,10 +528,14 @@
           <t>What type of service needed</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please describe the service you are seeking</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -551,10 +555,14 @@
           <t>Contact Method</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>How would you like to be contacted?</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,18 +574,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>contact_method</t>
+          <t>client_email</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Contact Info</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,18 +597,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>client_phone</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,84 +620,100 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>service_details</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Service Details</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Describe your service details</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>service_needed</t>
+          <t>assigned_tool</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Service Needed</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Assigned Tool</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Which tool do you want assigned?</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>tool_assigned</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Tool Assigned</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Is the tool assigned?</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Time</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Any additional notes</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -699,23 +723,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>service_type</t>
+          <t>service_address</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Service Type</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Service Address</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Please provide your service address</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,363 +755,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>service_type</t>
+          <t>submitted_by</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Service Details</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Submitted By</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Who submitted this form?</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>client_name</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Client Name</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>client_email</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Client Email</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>client_phone</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Client Phone</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>service_description</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Service Description</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>service_price</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Service Price</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>service_address</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Service Address</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Assigned Tool</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Assigned Tool</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Assigned Tool</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Assigned Tool</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Assigned Tool</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Assigned Tool</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Assigned Tool</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>submitted_by</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Submitted By</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,12 +785,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,34 +813,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>contact_method_choices</t>
+          <t>service_needed_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>haircut</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Haircut</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>contact_method_choices</t>
+          <t>service_needed_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>haircolor</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Haircolor</t>
         </is>
       </c>
     </row>
@@ -1165,12 +852,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>hair_styling</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Hair styling</t>
         </is>
       </c>
     </row>
@@ -1182,80 +869,80 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>makeup</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Makeup</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>service_type_choices</t>
+          <t>contact_method_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>service_type_choices</t>
+          <t>contact_method_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>service_type_choices</t>
+          <t>contact_method_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>in_person</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>In person</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>service_type_choices</t>
+          <t>assigned_tool_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>scissors</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Scissors</t>
         </is>
       </c>
     </row>
@@ -1267,12 +954,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>hair_dryer</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Hair dryer</t>
         </is>
       </c>
     </row>
@@ -1284,46 +971,46 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>makeup_brush</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Makeup brush</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>tool_assigned_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>tool_assigned_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1022,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>self</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Self</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1039,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>staff</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Staff</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>submitted_by_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>manager</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Manager</t>
         </is>
       </c>
     </row>
